--- a/gd/excel/Quest.xlsx
+++ b/gd/excel/Quest.xlsx
@@ -713,38 +713,140 @@
     <row r="2" ht="38" customHeight="1">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Id
-int32</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Id
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF8A5A00"/>
+              <sz val="9"/>
+            </rPr>
+            <t>int32</t>
+          </r>
         </is>
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>Title
-string</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Title
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>string</t>
+          </r>
         </is>
       </c>
       <c r="C2" s="6" t="inlineStr">
         <is>
-          <t>Description
-string</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Description
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>string</t>
+          </r>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>RewardItemId
-int32</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">RewardItemId
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>int32</t>
+          </r>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>RequiredLevel
-int32</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">RequiredLevel
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF64748B"/>
+              <sz val="9"/>
+            </rPr>
+            <t>int32</t>
+          </r>
         </is>
       </c>
       <c r="F2" s="18" t="inlineStr">
         <is>
-          <t>Test
-vector&lt;double&gt;[3]</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">Test
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF315B9A"/>
+              <sz val="9"/>
+            </rPr>
+            <t>vector&lt;double&gt;[3]</t>
+          </r>
         </is>
       </c>
       <c r="G2" s="16" t="n"/>
@@ -780,20 +882,71 @@
       <c r="E4" s="12" t="n"/>
       <c r="F4" s="13" t="inlineStr">
         <is>
-          <t>#1
-double</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">#1
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF6B4AA1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>double</t>
+          </r>
         </is>
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
-          <t>#2
-double</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">#2
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF6B4AA1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>double</t>
+          </r>
         </is>
       </c>
       <c r="H4" s="14" t="inlineStr">
         <is>
-          <t>#3
-double</t>
+          <r>
+            <rPr>
+              <rFont val="Aptos"/>
+              <b val="1"/>
+              <color rgb="FF172033"/>
+              <sz val="11"/>
+            </rPr>
+            <t xml:space="preserve">#3
+</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Consolas"/>
+              <i val="1"/>
+              <color rgb="FF6B4AA1"/>
+              <sz val="9"/>
+            </rPr>
+            <t>double</t>
+          </r>
         </is>
       </c>
     </row>
@@ -875,8 +1028,9 @@
       <formula1>-2147483648</formula1>
       <formula2>2147483647</formula2>
     </dataValidation>
-    <dataValidation sqref="D5:D1048576" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="引用" prompt="目标：Item.Id；最终以 canonical 校验为准" type="custom">
-      <formula1>TRUE</formula1>
+    <dataValidation sqref="D5:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
+      <formula1>-2147483648</formula1>
+      <formula2>2147483647</formula2>
     </dataValidation>
     <dataValidation sqref="E5:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="whole" operator="between">
       <formula1>-2147483648</formula1>
